--- a/consulting_forms/038_personal_training_consultation_form--consulting_forms.xlsx
+++ b/consulting_forms/038_personal_training_consultation_form--consulting_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Session Time</t>
+          <t>Preferred Time</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Goal List</t>
+          <t>Select Multiple Goal List</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Train List</t>
+          <t>Select Multiple Train List</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Assigned User Email</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Assigned User Phone</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Assigned User Notes</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1420,46 +1420,46 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one_train_choices</t>
+          <t>select_multiple_train_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one_train_choices</t>
+          <t>select_multiple_train_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Option 5</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1471,165 +1471,63 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_multiple_train_choices</t>
+          <t>select_multiple_train_list_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_multiple_train_choices</t>
+          <t>select_multiple_train_list_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_multiple_train_choices</t>
+          <t>select_multiple_train_list_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Option 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple_train_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>option_5</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Option 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple_train_list_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple_train_list_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>select_multiple_train_list_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>select_multiple_train_list_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>option_4</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Option 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>select_multiple_train_list_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>option_5</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Option 5</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
